--- a/www/download/COUNTRY.CZE.EXI382.xlsx
+++ b/www/download/COUNTRY.CZE.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>República Tcheca</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.134</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5.01</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4.908</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>5.096</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.859</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.757</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.873</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.748</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4.829</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4.923</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>4.989</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>5.093</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>5.204</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>5.11</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>5.057</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.918</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>5.065</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>4.752</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>4.594</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4.859</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>4.944</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>5.262</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>5.686</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>6.035</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>6.127</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5.646</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4.409</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>4.326</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>4.479</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>4.265</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4.204</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4.155</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4.061</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>4.12</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>4.053</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>4.18</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>4.234</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4.445</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>4.336</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>4.251</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>4.107</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>4.255</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>3.986</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>3.851</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>4.074</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>4.155</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>4.424</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>4.778</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>5.066</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>5.142</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>12305.186</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>9325.123</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>9082.699</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>9466.723</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>9400.914</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>9277.541</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>9211.65</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>8655.611</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>8852.681</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>8560.248</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>8773.855</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>8944.482</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>8975.089</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>9087.596</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>9313.63</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>9089.582</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>9101.091</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>8886.894</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>8994.842</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>8484.527</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>8208.031</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8739.988</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>8915.057</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>9532.349</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>10343.116</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10997.256</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>11175.184</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9858.675</t>
+          <t>19839255899.1155</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6316.248</t>
+          <t>15482584868.8047</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6095.142</t>
+          <t>15983179904.5914</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6389.505</t>
+          <t>15720402584.0134</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5834.972</t>
+          <t>15661632010.7135</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5908.615</t>
+          <t>16239534493.5882</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7504.379</t>
+          <t>16547704145.5874</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5564.327</t>
+          <t>16675332601.8651</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7062.057</t>
+          <t>16687122356.3312</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6744.539</t>
+          <t>17506671747.4384</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6969.614</t>
+          <t>18850756593.9684</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7215.308</t>
+          <t>20139419982.6406</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>7246.877</t>
+          <t>19258184969.5821</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7395.33</t>
+          <t>20719747907.3105</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7603.847</t>
+          <t>18359213857.3285</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>7406.866</t>
+          <t>19435563749.545</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>7361.172</t>
+          <t>19663778273.3602</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>7145.789</t>
+          <t>19271168938.0928</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>7355.161</t>
+          <t>19330287564.5177</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>6909.445</t>
+          <t>18169005639.4453</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>6668.707</t>
+          <t>17785360088.4956</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7102.463</t>
+          <t>18916237488.6766</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>7231.422</t>
+          <t>18524553049.4457</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7714.46</t>
+          <t>20236089593.206</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>8345.44</t>
+          <t>20816002953.28</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>8863.747</t>
+          <t>22386659210.9544</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>8996.475</t>
+          <t>22635273726.2806</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4047461835.92609</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2652629505.4867</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3078571423.76889</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2603947258.28856</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2643725407.03056</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2505402294.24144</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2693748380.27588</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2597973021.33514</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2585472246.885</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2970853366.24074</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3330102486.28807</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3787683000.44927</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3590862257.49047</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3451027489.58701</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3109979000.03755</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3339741529.15133</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2954756012.95388</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>3215126579.33335</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>3098959950.23908</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3014108505.01965</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>3509889930.47028</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3753393093.63725</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>3238488611.50341</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3601554048.11415</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>4272502707.00078</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>4704917955.09319</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4594604481.29168</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>66520665.1709219</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20347781.6911803</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>19972848.9772322</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>17545855.3581079</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>17773143.0220776</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>15373074.3368307</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>14383728.1335876</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>13427083.1433354</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>12687109.5488662</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>11206984.6090954</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>10221756.6816042</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>9777570.85873019</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>7947936.91168166</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>7300973.22068225</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>8359747.02570845</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>7656075.39108601</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>7015575.46003894</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7215572.91318761</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>7182434.42863014</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>8690186.25737438</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>10353955.3861315</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7317940.11147282</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>58268095.5511986</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8811911.3471347</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>7916740.51394275</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>8172260.25004845</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>10014369.7772623</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>27170.5600447157</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>44766.3560560405</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>49992.2574830695</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>50616.9077095101</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52986.3980757474</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>61716.7913816182</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>61009.9267423383</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>54550.9557432198</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>51483.6527919544</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>49410.102399751</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>53878.1128651103</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>58537.9099843886</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>60310.7250489565</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>61096.5657123465</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>62211.598445127</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>68742.1261994176</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>71749.4540145531</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>77078.907335484</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>77537.6830884295</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>75633.8623238449</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>83299.7893752898</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>81156.5109148843</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>87122.9159245912</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>89649.2174263913</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>102959.558905633</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>104882.44637927</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>104764.32954206</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>73952.8626956614</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>117653.283815901</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>132286.770695947</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>133763.978411874</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>140567.765073494</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>174230.936413253</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>178264.304358824</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>174134.440374076</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>160075.919483385</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>164114.925073031</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>189445.801585511</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>216505.006047818</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>214495.97234633</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>231885.25613643</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>205901.320808156</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>251367.13764433</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>264759.221570503</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>286395.569455505</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>280617.383448048</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>273011.818186583</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>301891.319060504</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>292661.391156784</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>303007.793460782</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>321924.91451976</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>352828.559305866</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>360972.724252553</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>358331.326015954</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.43576726248856</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.38112709933139</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.979860513529847</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1.45377665759577</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1.20710213870216</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.35834980018233</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.78585002777158</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.14179554533279</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.73143794465768</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.27023624815764</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.09291276430646</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.904939774301242</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.01814396664307</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.14293569735833</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.44498339053395</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.21779617834133</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.49129605548828</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.22255293024322</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.37342886584656</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.29236758248734</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.899976032993014</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.892278038208293</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.23296204064317</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.14198091639837</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.953290796297291</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.883932416753558</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.958052160367661</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>716.85721285207</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>601.668645779036</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>711.69027286732</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>581.324777213304</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>619.89202043682</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>595.891575670138</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>648.328624114185</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>639.715050852623</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>627.606700810512</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>748.289784104065</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>821.663233623356</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>906.079012120759</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>848.083992937919</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>797.040117656115</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>699.659077010175</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>770.214631878527</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>695.007438241184</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>782.874968791651</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>728.250137353934</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>756.102236191744</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>911.46079892244</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>921.416474771589</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>779.475459211133</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>814.172457925029</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>894.251487111675</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>928.691262202696</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>893.520413599321</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>687038328.036922</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>673137671.99595</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>218210877.503085</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>203415168.117326</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>250370821.853762</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>189008400.431678</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>482464962.452117</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>763555019.08026</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>730389539.498554</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1642702626.24282</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1854477141.70386</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>2035012314.48537</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>1753508573.78811</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>2545370022.00361</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>2653613517.82481</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>2708702731.13665</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>2619692359.52118</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>2778217773.8695</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>2697579460.94928</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>2697126762.68261</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>2711549048.31238</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>3436729763.19643</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>2993468409.72056</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>3330554166.97402</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>3138969625.18826</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>3563453305.50573</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>3108127943.95186</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1334732169.12892</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>726068512.447658</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>311002144.553042</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>351653700.656474</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>451561175.24187</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>472649150.967632</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>622496242.892361</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1126503407.69628</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>952921909.487683</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1941543984.87457</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2080316710.41749</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2206138926.00119</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1826789388.5591</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2533771726.49099</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2671071681.91821</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2730843338.69535</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2733329974.82809</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2921607529.59442</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2892035569.18691</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2870445073.83169</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2885975865.47698</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>3615045733.53192</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>3200532813.7006</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>3576501941.04737</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>3320217237.01489</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>3823046428.07999</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>4756100415.97063</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-647693841.091994</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-52930840.4517077</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-92791267.0499568</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-148238532.539148</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-201190353.388108</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-283640750.535953</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-140031280.440244</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-362948388.616016</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-222532369.989129</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-298841358.631755</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-225839568.713632</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-171126611.515816</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-73280814.7709911</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>11598295.512626</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-17458164.0933952</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-22140607.5586956</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-113637615.306913</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-143389755.724912</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-194456108.237629</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-173318311.14908</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-174426817.164603</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-178315970.335497</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-207064403.980038</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-245947774.073347</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-181247611.826625</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-259593122.574259</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-1647972472.01877</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>1746.09733094387</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>1432.64951728248</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>1409.04746911329</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>1426.44116880807</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>1368.16500407051</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>1405.320778412</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1806.14631549361</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>1370.13884619849</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1714.26875691525</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>1698.7945919991</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>1719.66946961165</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>1726.02594884841</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>1711.55559355423</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>1708.00572035197</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>1710.65482232619</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>1708.17906708277</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>1731.46928942528</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>1739.98105590195</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>1728.44989755255</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>1733.26425529214</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>1731.7536729653</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>1743.57615925358</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>1740.53911203137</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1743.94186753257</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>1746.7331993504</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>1749.59157401944</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>1749.55957618076</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1825.66763271841</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1861.15600113614</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1850.56163544251</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1857.68266586364</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1850.58965077633</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1893.49086944494</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1895.65827958979</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1819.53600167081</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1816.62618629802</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1802.96824003418</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1816.95219145807</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>1817.00916581281</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>1798.98383977334</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>1784.28055132234</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>1789.67882693579</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1778.74836108908</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1799.61583796396</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1807.13802615943</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>1776.01097177443</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>1785.59319919954</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>1786.87477037321</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1798.55789312927</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>1803.32644545961</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>1811.46906828727</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>1819.1522517728</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>1822.23648558493</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1823.91014369549</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>19305.6179497135</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20342.474838283</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>22952.3755895018</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>26056.0779409919</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>27514.031411336</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>34602.198439715</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>39924.6402003251</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>41264.6165994784</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>41854.6041286333</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>57028.3983673248</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>71948.3585680288</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>84287.6846619253</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>92604.734181172</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>100424.249109622</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>88875.5734800562</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>105828.598793287</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>118073.90012827</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>128374.720001682</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>124599.645901906</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>132389.984432411</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>143931.386954385</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>148178.564044304</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>160482.198798677</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>167648.277724738</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>173344.42954139</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>182276.759648888</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>188665.749706118</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3695718649.44048</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2734907338.57373</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2815728489.4883</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3038016603.70855</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3197045934.82714</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3713824956.5826</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3599679922.33354</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>3497179822.6004</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>3476802493.58652</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>4396280307.22409</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>5276909232.09657</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5507260312.19701</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>5349316727.28407</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>5564857184.75476</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>5180691553.29118</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>5529537264.21589</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>5946676538.74078</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>6062844998.64508</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>6325760633.16627</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>6084797993.51788</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>6020463131.05307</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>6691083401.4726</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>6585113567.35953</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>7166063453.85882</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>7193811615.65068</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>7874632088.44797</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>7837718260.68809</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>21149.4678031399</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>23696.3170609123</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>25922.247833843</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>26299.8930468831</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>27896.8046613777</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>36234.5247960077</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>41211.504705275</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>42772.6965070688</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>43610.7909158731</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>56238.8011144263</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>68590.9648026974</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>79855.9039519884</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>88207.5921499306</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>95873.5207905941</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>81301.5022683597</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>99522.4584206001</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>109918.094479476</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>118246.096455949</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>112727.965949575</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>119334.714866385</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>130759.759563531</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>130487.170395476</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>141442.326446076</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>151271.463052515</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>155696.457686366</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>165406.984301661</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>172137.176457832</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12305.186</t>
+          <t>5427346301.5075</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9325.123</t>
+          <t>4089337975.71436</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>9082.699</t>
+          <t>3589862972.74555</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>9466.723</t>
+          <t>3287366128.29476</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>9400.914</t>
+          <t>3517634171.74981</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9277.541</t>
+          <t>4156073412.03604</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9211.65</t>
+          <t>4289689090.55535</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8655.611</t>
+          <t>4513087207.42957</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8852.681</t>
+          <t>4505528929.91995</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8560.248</t>
+          <t>5894178818.29082</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8773.855</t>
+          <t>6569860304.76744</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8944.482</t>
+          <t>6882860442.62253</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>8975.089</t>
+          <t>6556777632.8238</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>9087.596</t>
+          <t>7486598358.40798</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>9313.63</t>
+          <t>6719466850.14445</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>9089.582</t>
+          <t>7460680171.79496</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>9101.091</t>
+          <t>7625876009.73427</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>8886.894</t>
+          <t>7736726473.46816</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>8994.842</t>
+          <t>7663396930.28897</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>8484.527</t>
+          <t>7394070061.55956</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>8208.031</t>
+          <t>7458778353.41105</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>8739.988</t>
+          <t>8251525312.60933</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>8915.057</t>
+          <t>7744608978.71039</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>9532.349</t>
+          <t>8868930822.80729</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>10343.116</t>
+          <t>8722096626.74787</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10997.256</t>
+          <t>9801020017.73046</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>11175.184</t>
+          <t>9335383447.31144</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9858.675</t>
+          <t>-1843.84985342642</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6316.248</t>
+          <t>-3353.84222262928</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6095.142</t>
+          <t>-2969.87224434129</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6389.505</t>
+          <t>-243.815105891182</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5834.972</t>
+          <t>-382.773250041769</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5908.615</t>
+          <t>-1632.32635629269</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7504.379</t>
+          <t>-1286.8645049499</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5564.327</t>
+          <t>-1508.07990759046</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7062.057</t>
+          <t>-1756.18678723987</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6744.539</t>
+          <t>789.597252898541</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6969.614</t>
+          <t>3357.39376533144</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7215.308</t>
+          <t>4431.78070993691</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>7246.877</t>
+          <t>4397.1420312414</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>7395.33</t>
+          <t>4550.72831902831</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>7603.847</t>
+          <t>7574.07121169653</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>7406.866</t>
+          <t>6306.14037268685</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>7361.172</t>
+          <t>8155.80564879467</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>7145.789</t>
+          <t>10128.6235457326</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>7355.161</t>
+          <t>11871.6799523311</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>6909.445</t>
+          <t>13055.2695660261</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>6668.707</t>
+          <t>13171.6273908545</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>7102.463</t>
+          <t>17691.3936488276</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>7231.422</t>
+          <t>19039.8723526008</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>7714.46</t>
+          <t>16376.8146722236</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>8345.44</t>
+          <t>17647.9718550244</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>8863.747</t>
+          <t>16869.7753472276</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>8996.475</t>
+          <t>16528.5732482862</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>14596.018</t>
+          <t>-1731627652.06702</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>11665.711</t>
+          <t>-1354430637.14062</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12031.779</t>
+          <t>-774134483.257254</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11823.191</t>
+          <t>-249349524.586217</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11718.829</t>
+          <t>-320588236.922672</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11995.088</t>
+          <t>-442248455.453438</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12153.136</t>
+          <t>-690009168.221809</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12221.114</t>
+          <t>-1015907384.82917</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>12297.928</t>
+          <t>-1028726436.33342</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>12806.671</t>
+          <t>-1497898511.06673</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>13643.81</t>
+          <t>-1292951072.67087</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>14456.249</t>
+          <t>-1375600130.42552</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>13946.313</t>
+          <t>-1207460905.53974</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>14931.489</t>
+          <t>-1921741173.65322</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>13526.596</t>
+          <t>-1538775296.85327</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>14068.688</t>
+          <t>-1931142907.57908</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>14196.172</t>
+          <t>-1679199470.99349</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>13957.672</t>
+          <t>-1673881474.82307</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>14018.027</t>
+          <t>-1337636297.1227</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>13150.408</t>
+          <t>-1309272068.04168</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>12856.224</t>
+          <t>-1438315222.35798</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>13660.782</t>
+          <t>-1560441911.13673</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>13543.439</t>
+          <t>-1159495411.35086</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14692.027</t>
+          <t>-1702867368.94847</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>15231.428</t>
+          <t>-1528285011.09719</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16344.146</t>
+          <t>-1926387929.28249</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>16465.913</t>
+          <t>-1497665186.62335</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>17134.5155924003</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>19666.4159815074</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>20788.6770202908</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>22513.8927557158</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>21724.8582347217</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>22091.1391000148</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>26854.5519003013</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>30362.5929827922</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>31166.4524345229</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>33607.9047181853</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>39440.5334744812</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>44310.3042641974</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>49119.4542189519</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>57854.6389937144</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>52044.0026143958</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>55760.0592649613</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>56772.101402917</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>57804.870767109</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>57172.8184608114</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>55570.6542942686</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>61399.6707925507</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>64428.5435585824</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>68817.8022639104</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>75235.2643605247</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>80588.4464153327</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>81544.4210613472</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>86103.5298135301</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>7289.017</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>5891.029</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>6040.175</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>5948.673</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>5903.583</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>5752.434</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5663.356</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>5223.868</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>5366.916</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>5270.736</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>5361.128</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>5445.23</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>5414.904</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>5459.189</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>5547.104</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>5315.102</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>5328.862</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>5186.535</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>5341.172</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>5033.453</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>4907.451</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>5245.57</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>5326.309</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>5635.319</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>6074.357</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>6504.557</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>6617.812</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23892.6509255471</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>26495.1831155095</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>30518.2093728689</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>30371.6097231001</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>30403.610157945</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>32187.8676495556</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>38337.2962842937</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>44509.5615156856</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45270.0771346559</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>49149.5036967326</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>58278.2319754728</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>66028.1595614725</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>73510.1433384987</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>85857.7211216228</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>76861.4030245589</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>82879.9423775327</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>82916.9184622124</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>85611.1147698549</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>83788.3688546218</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>80889.9944458741</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>87965.7414493917</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>92158.3921061505</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>99353.9665425821</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>110712.053934333</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>119214.185938358</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>119260.072569702</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>125297.774756873</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>3561.756</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2324.059</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2732.755</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2296.968</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2348.594</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2223.896</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2390.163</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2253.308</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2258.27</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2630.26</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2935.811</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>3309.784</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>3162.439</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>3006.041</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>2772.931</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2937.932</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>2585.315</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2825.325</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>2718.065</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>2676.899</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>3127.488</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>3352.428</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2924.883</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>3229.594</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>3848.752</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>4233.489</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>4102.771</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>176.79</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>171.78</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>123.04</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>178.17</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>148.45</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>165.69</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>213.97</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>146.94</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>212.72</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>156.42</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>137.4</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>129.15</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>146.02</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>174.22</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>152.11</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>184.73</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>152.92</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>170.6</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>158.11</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>113.23</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>111.86</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>147.24</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>138.87</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>116.83</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>109.37</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>119.28</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>70.253</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>20.117</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>19.695</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>17.37</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>17.436</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>14.857</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>13.975</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>12.839</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>12.167</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>10.809</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>9.838</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>9.284</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>7.611</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>8.035</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>7.231</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>6.652</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>6.814</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>6.845</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>8.52</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>10.544</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>7.038</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>65.091</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>8.828</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>7.943</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>8.128</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>10.263</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>26061.6805808453</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>30955.486646119</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>29232.1287815482</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>34131.2146702817</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>36031.1458142749</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>40565.5481736395</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>44301.3100293726</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>50564.2721957109</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>51233.9616017784</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>55243.7231602278</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>61426.7263378517</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>69233.3357470456</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>77009.0915289789</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>88613.2025668334</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>84272.2928944325</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>88434.4716819132</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>95827.4134694594</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>90940.8693176863</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>88784.1261776035</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>89336.4473791122</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>95218.8822298595</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>99297.919942555</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>109690.504034298</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>116457.019674562</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>122975.819013714</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>129146.060706928</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>129150.465320467</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>9858675036.12063</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6316248000.00041</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>6095142000.00138</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>6389504999.99897</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>5834971999.99839</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5908615000.00065</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7504379000.0012</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5564327043.99037</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7062057000.00103</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6744539000.00086</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6969614000.00098</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>7215308000.00049</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>7246877000.00071</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>7395330000.00089</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>7603847000.00119</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>7406865999.99964</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>7361172000.00228</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>7145789000.00019</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>7355160999.99984</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>6909444627.00642</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>6668706746.33705</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>7102463319.85244</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>7231422138.54233</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>7714460040.43781</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>8345440214.73988</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>8863747453.76591</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>8996475230.62811</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>12305186074.28</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>9325123000.00054</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>9082699000.00087</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>9466722999.99986</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>9400913999.99816</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9277540999.9997</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>9211650000.00095</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>8655610999.9979</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>8852681000.00122</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>8560248000.0002</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>8773855000.00094</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8944482000.00019</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>8975089000.00128</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>9087596000.00118</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>9313630000.00136</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>9089582000.00025</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>9101091000.00175</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>8886894000.00016</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>8994842000.00007</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>8484526622.42906</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>8208031214.23864</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>8739988324.18744</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>8915056618.94588</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>9532348629.10104</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>10343115740.3291</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10997256452.8583</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>11175184263.0297</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7289017273.98609</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5891029000.00063</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>6040175000.00126</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5948673000.00042</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>5903582999.99761</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5752433999.99965</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5663355999.99889</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5223867999.99868</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5366916000.00081</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5270736000.00022</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5361128000.00012</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5445229999.99931</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5414904000.00179</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>5459189000.00028</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5547104000.00061</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>5315102000.00157</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>5328862000.00072</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>5186534999.99931</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>5341171999.99932</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>5033452691.61868</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>4907450647.9547</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>5245570070.41597</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>5326308803.59312</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>5635319026.20078</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>6074356584.01485</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>6504556789.34119</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>6617811795.30257</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>6740102.00638638</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5010393.00000001</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4908077.00000167</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>5095984.99999932</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>5079955.99999947</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4899701.99999925</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4859341.00000045</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4757043.00000097</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4873144.00000007</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4747863.99999921</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4828885.99999987</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4922640.00000187</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4988977.00000021</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>5093142.9999987</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5204079.00000009</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5110099.9999994</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>5057241.00000058</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4917662.0000005</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>5064632.00000011</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4751657.11105563</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>4593512.28767099</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>4859442.31073983</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>4943673.1998203</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>5262219.92745028</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>5685678.99154646</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>6035032.52176854</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>6127047.59697606</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5646119.98507061</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4408787.99999973</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>4325718.00000254</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4479332.99999889</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>4264815.99999884</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4204459.99999896</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4154912.00000056</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4061141.00000073</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4119574.00000038</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3970190.99999844</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4052880.00000078</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4180301.00000205</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4234087.99999993</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4329803.99999886</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4444991.99999991</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>4336117.99999931</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>4251402.00000062</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>4106820.00000054</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>4255350.99999983</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>3986376.9219898</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>3850840.24965176</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>4073503.34664645</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>4154702.46463041</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>4423576.37261882</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>4777741.79699768</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>5066180.92210099</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>5142137.11445436</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>12305186074.28</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>9325123000.00054</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>9082699000.00087</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>9466722999.99986</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>9400913999.99816</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9277540999.9997</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9211650000.00095</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>8655610999.9979</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>8852681000.00122</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>8560248000.0002</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>8773855000.00094</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>8944482000.00019</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>8975089000.00128</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>9087596000.00118</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>9313630000.00136</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>9089582000.00025</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>9101091000.00175</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>8886894000.00016</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>8994842000.00007</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>8484526622.42906</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>8208031214.23864</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>8739988324.18744</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>8915056618.94588</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>9532348629.10104</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>10343115740.3291</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10997256452.8583</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>11175184263.0297</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>9858675036.12063</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6316248000.00041</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6095142000.00138</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6389504999.99897</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>5834971999.99839</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5908615000.00065</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7504379000.0012</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5564327043.99037</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7062057000.00103</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6744539000.00086</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>6969614000.00098</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7215308000.00049</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>7246877000.00071</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>7395330000.00089</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>7603847000.00119</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>7406865999.99964</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>7361172000.00228</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>7145789000.00019</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>7355160999.99984</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>6909444627.00642</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>6668706746.33705</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>7102463319.85244</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>7231422138.54233</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>7714460040.43781</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>8345440214.73988</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>8863747453.76591</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>8996475230.62811</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>118359.080492235</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>134155.221226511</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>142311.832033237</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>152588.503095332</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>154053.053593446</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>178691.762125545</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>204229.495604721</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>232925.144127347</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>238663.451121867</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>266127.19588495</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>310661.340638017</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>360563.353271981</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>401961.500427633</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>463922.475729894</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>399632.636798417</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>444490.09143236</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>470307.038360147</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>466629.282519669</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>454444.37211967</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>457191.417915088</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>491880.488897662</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>506574.300700546</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>552654.478038459</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>600873.422730636</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>635875.767550112</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>652068.923781696</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>673757.840640793</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>26082.9540793907</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>29230.8171605553</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>32948.3902244163</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>33445.008255105</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>33312.2803937688</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>35341.6007526238</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>41557.4000873706</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>48008.5891682908</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>49104.2546616194</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>53985.1802059316</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>63579.7749834471</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>71897.2911964587</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>80355.9463756802</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>93974.7898271657</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>84375.895073168</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>90403.359691912</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>91187.0546874407</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>93402.7279033571</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>91963.9268428209</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>89371.0557697606</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>96966.3176092888</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>101779.436427111</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>109770.608685164</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>122545.94550835</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>130951.552256181</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>131426.589869032</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>138316.937589771</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
